--- a/7203.T_report.xlsx
+++ b/7203.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,59 +449,343 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1781.62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1897.76</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2065</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1063122</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-11-21</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2564.64</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2536.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2115</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1049273</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3580.27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3414.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I4" t="n">
+        <v>998653</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>16.77%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2593.98</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2823.06</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2085</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1084761</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
-        </is>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>16.7日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2907.16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3167.62</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2267</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1179679</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1167703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3674.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3644.04</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2350</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1167703</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>167703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>12932</v>
       </c>
     </row>
   </sheetData>
